--- a/event_planner_forms/001_marathon_registration_form--event_planner_forms.xlsx
+++ b/event_planner_forms/001_marathon_registration_form--event_planner_forms.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +43,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -427,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -510,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>participant_info</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Participant Information</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -533,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Contact Information</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -556,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>participant_info_2</t>
+          <t>emergency_contact</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Participant Information</t>
+          <t>Emergency Contact</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -579,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>emergency_contact</t>
+          <t>medical_info</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Emergency Contact</t>
+          <t>Medical Information</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -597,23 +607,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>medical_info</t>
+          <t>participant_info</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Medical Information</t>
+          <t>Participant Information</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -648,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>participant_info_7</t>
+          <t>participant_info_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Participant Information</t>
+          <t>Additional Participant Info</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -671,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>emergency_contact_2</t>
+          <t>participant_info_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Emergency Contact</t>
+          <t>Participant Age</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -694,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>medical_info_2</t>
+          <t>participant_info_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Medical Information</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -712,366 +722,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>participant_info_8</t>
+          <t>participant_info_5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Participant Information</t>
+          <t>Registration Time</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>emergency_contact_3</t>
+          <t>participant_info_6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Emergency Contact</t>
+          <t>Participant Availability</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>medical_info_2</t>
+          <t>participant_info_7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Medical Information</t>
+          <t>Participant Notes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>participant_info_9</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Participant Information</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>emergency_contact_4</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Emergency Contact</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>medical_info_3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Medical Information</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>participant_info_10</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Participant Information</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>emergency_contact_5</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Emergency Contact</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>medical_info_4</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Medical Information</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>participant_info_11</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Participant Information</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>emergency_contact_6</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Emergency Contact</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>medical_info_5</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Medical Information</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>participant_info_12</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Participant Information</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>emergency_contact_7</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Emergency Contact</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>medical_info_6</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Medical Information</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>participant_info_13</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Participant Information</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1083,6 +794,110 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>list_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>participant_info_choices</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>participant_info_choices</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>participant_info_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>participant_info_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Option 4</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
